--- a/data/GTM_Final_report.xlsx
+++ b/data/GTM_Final_report.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
     <col width="11.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -638,12 +638,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wheeler</t>
+          <t>Fennell</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -651,27 +651,27 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>GTM import
 Score: 100 (HIGH)
-Role target: Managing Director
+Role target: CFO
 Source: apollo
-Person LinkedIn: http://linkedin.com/in/adam-wheeler-4a7a031b
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
+Person LinkedIn: http://linkedin.com/in/kevin-fennell-8188554
+Company LinkedIn: https://www.linkedin.com/company/broadstone-net-lease-inc
 Email confidence: from_apollo
 Phone source: apollo
 Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
+AUM: 6B
+Asset focus: Net Lease REIT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -681,12 +681,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>adam.wheeler@clarionpartners.com</t>
+          <t>kevin.fennell@broadstone.com</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>EVP, Chief Financial Officer</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -696,28 +696,28 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/adam-wheeler-4a7a031b</t>
+          <t>http://linkedin.com/in/kevin-fennell-8188554</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
+          <t>https://linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -726,12 +726,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bohdy</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hedgcock</t>
+          <t>Sauer 175b1317</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -739,27 +739,27 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>GTM import
 Score: 100 (HIGH)
-Role target: Managing Director
-Source: apollo
-Person LinkedIn: http://linkedin.com/in/bohdy-hedgcock-4084554
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
+Role target: CTO
+Source: tavily
+Person LinkedIn: https://linkedin.com/in/matt-sauer-175b1317
+Company LinkedIn: https://www.linkedin.com/company/broadstone-net-lease-inc
 Email confidence: from_apollo
 Phone source: apollo
 Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
+AUM: 6B
+Asset focus: Net Lease REIT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bohdy.hedgcock@clarionpartners.com</t>
+          <t>matt.sauer@broadstone.com</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Matt Sauer - Director - Broadstone Net Lease, Inc. | LinkedIn</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/bohdy-hedgcock-4084554</t>
+          <t>https://linkedin.com/in/matt-sauer-175b1317</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -800,12 +800,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
+          <t>https://linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -814,12 +814,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brent</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>Albano</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -827,27 +827,27 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>GTM import
 Score: 100 (HIGH)
-Role target: Managing Director
+Role target: COO
 Source: apollo
-Person LinkedIn: http://linkedin.com/in/bejenkins
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
+Person LinkedIn: http://linkedin.com/in/ryan-albano-51890111
+Company LinkedIn: https://www.linkedin.com/company/broadstone-net-lease-inc
 Email confidence: from_apollo
 Phone source: apollo
 Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
+AUM: 6B
+Asset focus: Net Lease REIT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>brent.jenkins@clarionpartners.com</t>
+          <t>ryan.albano@broadstone.com</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>President and COO</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/bejenkins</t>
+          <t>http://linkedin.com/in/ryan-albano-51890111</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
+          <t>https://linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -902,40 +902,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brett</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kahn</t>
-        </is>
-      </c>
+          <t>Jennielobrien</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>GTM import
-Score: 100 (HIGH)
-Role target: Managing Director
-Source: apollo
-Person LinkedIn: http://linkedin.com/in/brett-kahn-5338993
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
+Score: 95 (HIGH)
+Role target: CFO
+Source: tavily
+Person LinkedIn: https://linkedin.com/in/jennielobrien
+Company LinkedIn: https://www.linkedin.com/company/broadstone-net-lease-inc
 Email confidence: from_apollo
 Phone source: apollo
 Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
+AUM: 6B
+Asset focus: Net Lease REIT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -945,12 +941,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>brett.kahn@clarionpartners.com</t>
+          <t>jennie.obrien@broadstone.com</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Jennie O'Brien, CPA - SVP, Chief Accounting Officer at Broadstone Net Lease - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -960,28 +956,28 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/brett-kahn-5338993</t>
+          <t>https://linkedin.com/in/jennielobrien</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
+          <t>https://linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -990,40 +986,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brian</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Watkins</t>
-        </is>
-      </c>
+          <t>Lynnecody</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>GTM import
-Score: 100 (HIGH)
-Role target: Managing Director
-Source: apollo
-Person LinkedIn: http://linkedin.com/in/brian-watkins-a02a9210
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
+Score: 95 (HIGH)
+Role target: CTO
+Source: tavily
+Person LinkedIn: https://linkedin.com/in/lynnecody
+Company LinkedIn: https://www.linkedin.com/company/broadstone-net-lease-inc
 Email confidence: from_apollo
 Phone source: apollo
 Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
+AUM: 6B
+Asset focus: Net Lease REIT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Mendon</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1033,12 +1025,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>brian.watkins@clarionpartners.com</t>
+          <t>lynne.cody@broadstone.com</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Lynne Cody - Director, Due Diligence &amp; Transactions - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1048,12 +1040,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/brian-watkins-a02a9210</t>
+          <t>https://linkedin.com/in/lynnecody</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -1064,12 +1056,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
+          <t>https://linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -1078,12 +1070,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Elliott</t>
+          <t>Vinh</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Byers</t>
+          <t>Nguyen 58375a103</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1091,27 +1083,27 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>GTM import
-Score: 100 (HIGH)
-Role target: Managing Director
-Source: apollo
-Person LinkedIn: http://linkedin.com/in/elliott-byers-7a93114b
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
+Score: 85 (HIGH)
+Role target: CTO
+Source: tavily
+Person LinkedIn: https://linkedin.com/in/vinh-nguyen-58375a103
+Company LinkedIn: https://www.linkedin.com/company/broadstone-net-lease-inc
 Email confidence: from_apollo
 Phone source: apollo
 Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
+AUM: 6B
+Asset focus: Net Lease REIT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Fairport</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1121,12 +1113,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>elliott.byers@clarionpartners.com</t>
+          <t>vinh.nguyen@broadstone.com</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Vinh Nguyen - Director, Information Technology at Broadstone Net ...</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1136,28 +1128,28 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/elliott-byers-7a93114b</t>
+          <t>https://linkedin.com/in/vinh-nguyen-58375a103</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
+          <t>https://linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1166,12 +1158,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Evans</t>
+          <t>Erica</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Walter Arm A0076b169</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -1179,27 +1171,27 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>GTM import
-Score: 100 (HIGH)
-Role target: Managing Director
-Source: apollo
-Person LinkedIn: http://linkedin.com/in/evans-k-anderson-jr-4522609
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
+Score: 80 (HIGH)
+Role target: CTO
+Source: tavily
+Person LinkedIn: https://linkedin.com/in/erica-walter-arm-a0076b169
+Company LinkedIn: https://www.linkedin.com/company/broadstone-net-lease-inc
 Email confidence: from_apollo
 Phone source: apollo
 Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
+AUM: 6B
+Asset focus: Net Lease REIT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1209,12 +1201,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>evans.anderson@clarionpartners.com</t>
+          <t>erica.walter@broadstone.com</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Erica Walter, ARM - -- - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1224,12 +1216,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/evans-k-anderson-jr-4522609</t>
+          <t>https://linkedin.com/in/erica-walter-arm-a0076b169</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -1240,12 +1232,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
+          <t>https://linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1254,12 +1246,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Glenn</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Roethel 26381a149</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -1267,27 +1259,27 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>GTM import
-Score: 100 (HIGH)
+Score: 70 (HIGH)
 Role target: Managing Director
-Source: apollo
-Person LinkedIn: http://linkedin.com/in/glenn-johnson-boston
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
+Source: tavily
+Person LinkedIn: https://linkedin.com/in/laura-roethel-26381a149
+Company LinkedIn: https://www.linkedin.com/company/broadstone-net-lease-inc
 Email confidence: from_apollo
 Phone source: apollo
 Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
+AUM: 6B
+Asset focus: Net Lease REIT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,12 +1289,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>glenn.johnson@clarionpartners.com</t>
+          <t>laura.roethel@broadstone.com</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Laura Roethel - Broadstone Net Lease, Inc. - LinkedIn</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1312,28 +1304,28 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/glenn-johnson-boston</t>
+          <t>https://linkedin.com/in/laura-roethel-26381a149</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
+          <t>https://linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1342,12 +1334,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hopkins</t>
+          <t>Morsch B4b02930</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -1355,27 +1347,27 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>GTM import
-Score: 100 (HIGH)
-Role target: Partner
-Source: apollo
-Person LinkedIn: http://linkedin.com/in/heather-hopkins-217a0bb
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
+Score: 70 (HIGH)
+Role target: Managing Director
+Source: tavily
+Person LinkedIn: https://linkedin.com/in/matthew-morsch-b4b02930
+Company LinkedIn: https://www.linkedin.com/company/broadstone-net-lease-inc
 Email confidence: from_apollo
 Phone source: apollo
 Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
+AUM: 6B
+Asset focus: Net Lease REIT</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Garrison</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,12 +1377,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>heather.hopkins@clarionpartners.com</t>
+          <t>matthew.morsch@broadstone.com</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Fund CFO</t>
+          <t>Matthew Morsch - Senior Manager, Property Management, Industrial at Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1400,12 +1392,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/heather-hopkins-217a0bb</t>
+          <t>https://linkedin.com/in/matthew-morsch-b4b02930</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -1416,12 +1408,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
+          <t>https://linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -1430,12 +1422,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Glasser</t>
+          <t>Caruso 17537083</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -1443,27 +1435,27 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>GTM import
-Score: 100 (HIGH)
+Score: 70 (HIGH)
 Role target: Managing Director
-Source: apollo
-Person LinkedIn: http://linkedin.com/in/jason-glasser-52a73ab6
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
+Source: tavily
+Person LinkedIn: https://linkedin.com/in/michael-caruso-17537083
+Company LinkedIn: https://www.linkedin.com/company/broadstone-net-lease-inc
 Email confidence: from_apollo
 Phone source: apollo
 Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
+AUM: 6B
+Asset focus: Net Lease REIT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1473,12 +1465,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>jason.glasser@clarionpartners.com</t>
+          <t>michael.caruso@broadstone.com</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Michael Caruso - Broadstone Net Lease, Inc. - LinkedIn</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1488,12 +1480,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/jason-glasser-52a73ab6</t>
+          <t>https://linkedin.com/in/michael-caruso-17537083</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -1504,12 +1496,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
+          <t>https://linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1518,12 +1510,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deberadinis</t>
+          <t>Delemos 722b1722</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -1531,27 +1523,27 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>GTM import
-Score: 100 (HIGH)
+Score: 70 (HIGH)
 Role target: Managing Director
-Source: apollo
-Person LinkedIn: http://linkedin.com/in/john-deberadinis-782b4942
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
+Source: tavily
+Person LinkedIn: https://linkedin.com/in/sam-delemos-722b1722
+Company LinkedIn: https://www.linkedin.com/company/broadstone-net-lease-inc
 Email confidence: from_apollo
 Phone source: apollo
 Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
+AUM: 6B
+Asset focus: Net Lease REIT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Nashville</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1561,12 +1553,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>john.deberadinis@clarionpartners.com</t>
+          <t>sam.delemos@broadstone.com</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Managing Director, Fund CFO</t>
+          <t>Sam DeLemos - Real Estate Investment Professional - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1576,28 +1568,28 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/john-deberadinis-782b4942</t>
+          <t>https://linkedin.com/in/sam-delemos-722b1722</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
+          <t>https://linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1606,12 +1598,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Christina</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kane</t>
+          <t>Ingerson 63149414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1619,27 +1611,27 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>GTM import
-Score: 100 (HIGH)
+Score: 60 (MEDIUM)
 Role target: Managing Director
-Source: apollo
-Person LinkedIn: http://linkedin.com/in/josh-kane-45361017
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
+Source: tavily
+Person LinkedIn: https://linkedin.com/in/christina-ingerson-63149414
+Company LinkedIn: https://www.linkedin.com/company/broadstone-net-lease-inc
 Email confidence: from_apollo
 Phone source: apollo
 Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
+AUM: 6B
+Asset focus: Net Lease REIT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1649,12 +1641,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>josh.kane@clarionpartners.com</t>
+          <t>christina.ingerson@broadstone.com</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Christina Ingerson - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1664,12 +1656,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/josh-kane-45361017</t>
+          <t>https://linkedin.com/in/christina-ingerson-63149414</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1680,12 +1672,12 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
+          <t>https://linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1694,12 +1686,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kasteel</t>
+          <t>Callan 83265954</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1707,27 +1699,27 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Clarion Partners</t>
+          <t>Broadstone Net Lease</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>GTM import
-Score: 100 (HIGH)
+Score: 60 (MEDIUM)
 Role target: Managing Director
-Source: apollo
-Person LinkedIn: http://linkedin.com/in/karen-kasteel
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
+Source: tavily
+Person LinkedIn: https://linkedin.com/in/john-callan-83265954
+Company LinkedIn: https://www.linkedin.com/company/broadstone-net-lease-inc
 Email confidence: from_apollo
 Phone source: apollo
 Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
+AUM: 6B
+Asset focus: Net Lease REIT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Rochester</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1737,12 +1729,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>karen.kasteel@clarionpartners.com</t>
+          <t>john.callan@broadstone.com</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>John Callan - Broadstone Net Lease, Inc.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1752,12 +1744,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>http://linkedin.com/in/karen-kasteel</t>
+          <t>https://linkedin.com/in/john-callan-83265954</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>+1 212-883-2500</t>
+          <t>+1 585-287-6500</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1768,192 +1760,16 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>https://www.clarionpartners.com</t>
+          <t>https://www.broadstone.com</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
+          <t>https://linkedin.com/company/broadstone-net-lease-inc</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Bishop</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Clarion Partners</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>GTM import
-Score: 100 (HIGH)
-Role target: Managing Director
-Source: apollo
-Person LinkedIn: http://linkedin.com/in/kevin-bishop-cfa-baba934
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
-Email confidence: from_apollo
-Phone source: apollo
-Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>kevin.bishop@clarionpartners.com</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>http://linkedin.com/in/kevin-bishop-cfa-baba934</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>+1 212-883-2500</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Massachusetts</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>https://www.clarionpartners.com</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Khalid</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rashid</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Clarion Partners</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>GTM import
-Score: 100 (HIGH)
-Role target: Managing Director
-Source: apollo
-Person LinkedIn: http://linkedin.com/in/krashid2008
-Company LinkedIn: https://www.linkedin.com/company/clarion-partners-llc
-Email confidence: from_apollo
-Phone source: apollo
-Country: USA
-AUM: 26B
-Asset focus: Diversified Real Estate</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>khalid.rashid@clarionpartners.com</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Managing Director</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>lead</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>http://linkedin.com/in/krashid2008</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>+1 212-883-2500</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>https://www.clarionpartners.com</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/company/clarion-partners-llc</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
